--- a/main_hw/SUMEC_MK_IV/bom/MK_IV bom.xlsx
+++ b/main_hw/SUMEC_MK_IV/bom/MK_IV bom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MenMe\GitHub\Sumec-MiniSumo\-PCB-\SUMEC_MK_IV\bom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MenMe\Documents\GitHub\Sumec-MiniSumo-HW\main_hw\SUMEC_MK_IV\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9842C37B-DA70-47D7-A755-5D5A05DCDF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sumecBOM" sheetId="1" r:id="rId1"/>
@@ -1487,22 +1487,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J76"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43" style="1" customWidth="1"/>
-    <col min="2" max="2" width="49.54296875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="49.5546875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="55" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.1796875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.26953125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.54296875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="36.81640625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="1"/>
+    <col min="6" max="6" width="37.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="36.77734375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>86</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>116</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>52</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>117</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>118</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>113</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>119</v>
       </c>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>111</v>
       </c>
@@ -1673,7 +1673,7 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D10" s="1" t="s">
         <v>88</v>
       </c>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D11" s="1" t="s">
         <v>89</v>
       </c>
@@ -1698,7 +1698,7 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D12" s="1" t="s">
         <v>87</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>109</v>
       </c>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="G13" s="9"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>46</v>
       </c>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>106</v>
       </c>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>105</v>
       </c>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>103</v>
       </c>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>101</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>100</v>
       </c>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>92</v>
       </c>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>40</v>
       </c>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>43</v>
       </c>
@@ -1934,7 +1934,7 @@
       <c r="F23" s="7"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>120</v>
       </c>
@@ -1953,7 +1953,7 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>121</v>
       </c>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>128</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>98</v>
       </c>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>122</v>
       </c>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>123</v>
       </c>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>97</v>
       </c>
@@ -2075,7 +2075,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>96</v>
       </c>
@@ -2094,7 +2094,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>47</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>124</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>11</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>18</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>15</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>6</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C38" s="1">
         <v>3</v>
       </c>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="I38" s="7"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C39" s="1">
         <v>2</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C40" s="1">
         <v>6</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C41" s="1">
         <v>100</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E42" s="7" t="s">
         <v>141</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="11"/>
     </row>
   </sheetData>
